--- a/survey_templates/041_vertical_selling_survey--survey_templates.xlsx
+++ b/survey_templates/041_vertical_selling_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>vertical_selling_survey_page_1</t>
+          <t>sales_and_marketing_role</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vertical Selling Survey</t>
+          <t>What is your role in the company?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sales and Marketing Strategy</t>
+          <t>What is your company's sales and marketing strategy?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>targeted_strategy</t>
+          <t>specific_vertical_market</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Targeted Strategy</t>
+          <t>Specific Vertical Market</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>specific_vertical_market</t>
+          <t>sales_and_marketing_budget</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Specific Vertical Market</t>
+          <t>What is your company's sales and marketing budget?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sales_and_marketing_budget</t>
+          <t>specific_sales_channels</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sales and Marketing Budget</t>
+          <t>Specific Sales Channels</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>marketing_strategy</t>
+          <t>specific_marketing_channels</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Marketing Strategy</t>
+          <t>Specific Marketing Channels</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,40 +653,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sales_strategy</t>
+          <t>sales_and_marketing_team</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sales Strategy</t>
+          <t>Who is part of your sales and marketing team?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>specific_sales_channels</t>
+          <t>sales_and_marketing_budget_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Specific Sales Channels</t>
+          <t>How much do you allocate for sales and marketing?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>specific_marketing_channels</t>
+          <t>specific_sales_channels_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Specific Marketing Channels</t>
+          <t>Specific Sales Channels 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,23 +722,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sales_and_marketing_team</t>
+          <t>specific_marketing_channels_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sales and Marketing Team</t>
+          <t>Specific Marketing Channels 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sales_and_marketing_budget</t>
+          <t>sales_and_marketing_team_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sales and Marketing Budget</t>
+          <t>How many team members do you have for sales and marketing?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Marketing Strategy</t>
+          <t>What is your marketing strategy?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sales Strategy</t>
+          <t>What is your sales strategy?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>specific_sales_channels</t>
+          <t>sales_and_marketing_alignment</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Specific Sales Channels</t>
+          <t>How do you align your sales and marketing efforts?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>specific_marketing_channels</t>
+          <t>sales_and_marketing_budget_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Specific Marketing Channels</t>
+          <t>Sales and Marketing Budget</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sales_and_marketing_team</t>
+          <t>marketing_strategy_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sales and Marketing Team</t>
+          <t>How do you measure the effectiveness of your marketing strategy?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sales_and_marketing_budget</t>
+          <t>sales_strategy_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sales and Marketing Budget</t>
+          <t>How do you measure the effectiveness of your sales strategy?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>marketing_strategy</t>
+          <t>specific_sales_channels_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Marketing Strategy</t>
+          <t>Specific Sales Channels 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,159 +929,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sales_strategy</t>
+          <t>specific_marketing_channels_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sales Strategy</t>
+          <t>Specific Marketing Channels 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>specific_sales_channels</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Specific Sales Channels</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>specific_marketing_channels</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Specific Marketing Channels</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>sales_and_marketing_team</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Sales and Marketing Team</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>sales_and_marketing_budget</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Sales and Marketing Budget</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>marketing_strategy</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Marketing Strategy</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>sales_strategy</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Sales Strategy</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1101,9 +963,9 @@
   <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,102 +988,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>specific_vertical_market_choices</t>
+          <t>sales_and_marketing_role_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'automotive',_'value':_1}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Automotive', 'value': 1}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>specific_vertical_market_choices</t>
+          <t>sales_and_marketing_role_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'financial_services',_'value':_2}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Financial Services', 'value': 2}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>specific_vertical_market_choices</t>
+          <t>sales_and_marketing_role_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'real_estate',_'value':_3}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Real Estate', 'value': 3}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>specific_sales_channels_choices</t>
+          <t>specific_vertical_market_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email',_'value':_1}</t>
+          <t>automotive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Email', 'value': 1}</t>
+          <t>Automotive</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>specific_sales_channels_choices</t>
+          <t>specific_vertical_market_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'phone',_'value':_2}</t>
+          <t>financial_services</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Phone', 'value': 2}</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>specific_sales_channels_choices</t>
+          <t>specific_vertical_market_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'social_media',_'value':_3}</t>
+          <t>real_estate</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Social Media', 'value': 3}</t>
+          <t>Real Estate</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'online_advertising',_'value':_4}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Online Advertising', 'value': 4}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1250,63 +1112,63 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'print_advertising',_'value':_5}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Print Advertising', 'value': 5}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>specific_marketing_channels_choices</t>
+          <t>specific_sales_channels_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email',_'value':_1}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Email', 'value': 1}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>specific_marketing_channels_choices</t>
+          <t>specific_sales_channels_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'print_media',_'value':_2}</t>
+          <t>online_advertising</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Print Media', 'value': 2}</t>
+          <t>Online Advertising</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>specific_marketing_channels_choices</t>
+          <t>specific_sales_channels_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'online_media',_'value':_3}</t>
+          <t>print_advertising</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Online Media', 'value': 3}</t>
+          <t>Print Advertising</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'social_media',_'value':_4}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Social Media', 'value': 4}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1335,505 +1197,505 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'event',_'value':_5}</t>
+          <t>print_media</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Event', 'value': 5}</t>
+          <t>Print Media</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sales_and_marketing_team_choices</t>
+          <t>specific_marketing_channels_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sales',_'value':_1}</t>
+          <t>online_media</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sales', 'value': 1}</t>
+          <t>Online Media</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sales_and_marketing_team_choices</t>
+          <t>specific_marketing_channels_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'marketing',_'value':_2}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Marketing', 'value': 2}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sales_and_marketing_team_choices</t>
+          <t>specific_marketing_channels_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_3}</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both', 'value': 3}</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>specific_sales_channels_choices</t>
+          <t>sales_and_marketing_team_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email',_'value':_1}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Email', 'value': 1}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>specific_sales_channels_choices</t>
+          <t>sales_and_marketing_team_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'phone',_'value':_2}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Phone', 'value': 2}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>specific_sales_channels_choices</t>
+          <t>sales_and_marketing_team_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'social_media',_'value':_3}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Social Media', 'value': 3}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>specific_sales_channels_choices</t>
+          <t>specific_sales_channels_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'online_advertising',_'value':_4}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Online Advertising', 'value': 4}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>specific_sales_channels_choices</t>
+          <t>specific_sales_channels_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'print_advertising',_'value':_5}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Print Advertising', 'value': 5}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>specific_marketing_channels_choices</t>
+          <t>specific_sales_channels_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email',_'value':_1}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Email', 'value': 1}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>specific_marketing_channels_choices</t>
+          <t>specific_sales_channels_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'print_media',_'value':_2}</t>
+          <t>online_advertising</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Print Media', 'value': 2}</t>
+          <t>Online Advertising</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>specific_marketing_channels_choices</t>
+          <t>specific_sales_channels_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'online_media',_'value':_3}</t>
+          <t>print_advertising</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Online Media', 'value': 3}</t>
+          <t>Print Advertising</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>specific_marketing_channels_choices</t>
+          <t>specific_marketing_channels_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'social_media',_'value':_4}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Social Media', 'value': 4}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>specific_marketing_channels_choices</t>
+          <t>specific_marketing_channels_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'event',_'value':_5}</t>
+          <t>print_media</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Event', 'value': 5}</t>
+          <t>Print Media</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sales_and_marketing_team_choices</t>
+          <t>specific_marketing_channels_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sales',_'value':_1}</t>
+          <t>online_media</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sales', 'value': 1}</t>
+          <t>Online Media</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>sales_and_marketing_team_choices</t>
+          <t>specific_marketing_channels_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'marketing',_'value':_2}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Marketing', 'value': 2}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>sales_and_marketing_team_choices</t>
+          <t>specific_marketing_channels_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_3}</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both', 'value': 3}</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>specific_sales_channels_choices</t>
+          <t>sales_and_marketing_alignment_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email',_'value':_1}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Email', 'value': 1}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>specific_sales_channels_choices</t>
+          <t>sales_and_marketing_alignment_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'phone',_'value':_2}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Phone', 'value': 2}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>specific_sales_channels_choices</t>
+          <t>sales_and_marketing_alignment_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'social_media',_'value':_3}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Social Media', 'value': 3}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>specific_sales_channels_choices</t>
+          <t>specific_sales_channels_3_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'online_advertising',_'value':_4}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Online Advertising', 'value': 4}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>specific_sales_channels_choices</t>
+          <t>specific_sales_channels_3_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'print_advertising',_'value':_5}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Print Advertising', 'value': 5}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>specific_marketing_channels_choices</t>
+          <t>specific_sales_channels_3_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email',_'value':_1}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Email', 'value': 1}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>specific_marketing_channels_choices</t>
+          <t>specific_sales_channels_3_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'print_media',_'value':_2}</t>
+          <t>online_advertising</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Print Media', 'value': 2}</t>
+          <t>Online Advertising</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>specific_marketing_channels_choices</t>
+          <t>specific_sales_channels_3_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'online_media',_'value':_3}</t>
+          <t>print_advertising</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Online Media', 'value': 3}</t>
+          <t>Print Advertising</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>specific_marketing_channels_choices</t>
+          <t>specific_marketing_channels_3_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'social_media',_'value':_4}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Social Media', 'value': 4}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>specific_marketing_channels_choices</t>
+          <t>specific_marketing_channels_3_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'event',_'value':_5}</t>
+          <t>print_media</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Event', 'value': 5}</t>
+          <t>Print Media</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>sales_and_marketing_team_choices</t>
+          <t>specific_marketing_channels_3_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sales',_'value':_1}</t>
+          <t>online_media</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sales', 'value': 1}</t>
+          <t>Online Media</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>sales_and_marketing_team_choices</t>
+          <t>specific_marketing_channels_3_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'marketing',_'value':_2}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Marketing', 'value': 2}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>sales_and_marketing_team_choices</t>
+          <t>specific_marketing_channels_3_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_3}</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both', 'value': 3}</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
